--- a/solutions/demo/closing-engine/template_en.xlsx
+++ b/solutions/demo/closing-engine/template_en.xlsx
@@ -2064,7 +2064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -2080,8 +2080,9 @@
     <col width="18" customWidth="1" min="11" max="11"/>
     <col width="23" customWidth="1" min="12" max="12"/>
     <col width="15" customWidth="1" min="13" max="13"/>
-    <col width="16" customWidth="1" min="14" max="14"/>
-    <col width="28" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="51" customHeight="1">
@@ -2156,21 +2157,26 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
+          <t>Year-end adjustment</t>
+        </is>
+      </c>
+      <c r="N2" s="8" t="inlineStr">
+        <is>
           <t>Decided by</t>
         </is>
       </c>
-      <c r="N2" s="8" t="inlineStr">
+      <c r="O2" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="O2" s="8" t="inlineStr">
+      <c r="P2" s="8" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="102" customHeight="1">
+    <row r="3" ht="174" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>Entry number. Rows of one entry share it. E.g. ADJ-2026-06-01</t>
@@ -2233,15 +2239,20 @@
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
+          <t>Yes for a year-end adjustment (period 13). Date it on the last day of the fiscal year. Monthly figures keep it out of the year-end month and show it in its own column; the year-to-date figures include it.</t>
+        </is>
+      </c>
+      <c r="N3" s="6" t="inlineStr">
+        <is>
           <t>Who made this decision (name). [Required]</t>
         </is>
       </c>
-      <c r="N3" s="6" t="inlineStr">
+      <c r="O3" s="6" t="inlineStr">
         <is>
           <t>The day it was decided. If you cannot recall, use today’s date. [Required] E.g. 2026-05-01</t>
         </is>
       </c>
-      <c r="O3" s="6" t="inlineStr">
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>Why it is treated this way. May be empty, but it helps when you look back.</t>
         </is>
@@ -2310,15 +2321,20 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>settlement</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>by</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -2326,9 +2342,9 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A1:P1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation sqref="E5:E2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Month end"</formula1>
     </dataValidation>
@@ -2337,6 +2353,9 @@
     </dataValidation>
     <dataValidation sqref="K5:K2000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"対象外,課税仕入10%,課税売上10%,非課税仕入,非課税売上"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M5:M2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the dropdown" error="This column takes one value from the list." type="list">
+      <formula1>"Yes"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/solutions/demo/closing-engine/template_en.xlsx
+++ b/solutions/demo/closing-engine/template_en.xlsx
@@ -1842,7 +1842,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -1853,9 +1853,10 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="23" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="31" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="31" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="51" customHeight="1">
@@ -1910,21 +1911,26 @@
       </c>
       <c r="I2" s="8" t="inlineStr">
         <is>
+          <t>Paid on</t>
+        </is>
+      </c>
+      <c r="J2" s="8" t="inlineStr">
+        <is>
           <t>Decided by</t>
         </is>
       </c>
-      <c r="J2" s="8" t="inlineStr">
+      <c r="K2" s="8" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="K2" s="8" t="inlineStr">
+      <c r="L2" s="8" t="inlineStr">
         <is>
           <t>Reason</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="162" customHeight="1">
+    <row r="3" ht="174" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
         <is>
           <t>The number of the item to confirm (shown on the page and the workpaper). Normally filled in automatically.</t>
@@ -1967,15 +1973,20 @@
       </c>
       <c r="I3" s="6" t="inlineStr">
         <is>
+          <t>[Only when answering Done for a scheduled payment (social insurance, withholding, resident tax) that is not in the bank statement] The date it was actually paid. E.g. 2026-09-16. The tool uses it to check the due date.</t>
+        </is>
+      </c>
+      <c r="J3" s="6" t="inlineStr">
+        <is>
           <t>Who made this decision (name). [Required]</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>The day it was decided. If you cannot recall, use today’s date. [Required] E.g. 2026-05-01</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="L3" s="6" t="inlineStr">
         <is>
           <t>Why it is treated this way. May be empty, but it helps when you look back.</t>
         </is>
@@ -2024,15 +2035,20 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>paid_on</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>by</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>at</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>reason</t>
         </is>
@@ -2040,7 +2056,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A1:L1"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="B5:B2000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Choose from the dropdown" error="This column takes one value from the list." type="list">
